--- a/lecture/2026_05_20_14-411779280890_member_export_1030513.xlsx
+++ b/lecture/2026_05_20_14-411779280890_member_export_1030513.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/teaching/lecture/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B7DCEA-0A5E-EA4F-A685-732178B6CEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="19220" yWindow="1080" windowWidth="27900" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mitglieder" sheetId="1" r:id="rId4"/>
+    <sheet name="Mitglieder" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
-  <si>
-    <t>Rolle/Status</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Nachname</t>
   </si>
@@ -32,9 +34,6 @@
     <t>E-Mail</t>
   </si>
   <si>
-    <t>Gruppenmitglied</t>
-  </si>
-  <si>
     <t>Günther</t>
   </si>
   <si>
@@ -201,22 +200,26 @@
   </si>
   <si>
     <t>kendnewende.yameogo@hs-osnabrueck.de</t>
+  </si>
+  <si>
+    <t>Unterschrift der Teilnahme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -227,7 +230,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -235,18 +238,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -536,278 +570,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="43.561" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="E9" t="s">
+      <c r="B10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="E10" t="s">
+      <c r="B11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="s">
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>48</v>
       </c>
-      <c r="E12" t="s">
+      <c r="B13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>52</v>
       </c>
-      <c r="E13" t="s">
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E14" t="s">
+      <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
+      <c r="E15" s="3"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>